--- a/artfynd/A 58545-2025 artfynd.xlsx
+++ b/artfynd/A 58545-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130104789</v>
       </c>
       <c r="B2" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130104751</v>
       </c>
       <c r="B4" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130104750</v>
       </c>
       <c r="B5" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>130104757</v>
       </c>
       <c r="B6" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>130104743</v>
       </c>
       <c r="B7" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>130104765</v>
       </c>
       <c r="B8" t="n">
-        <v>91412</v>
+        <v>91414</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>130104791</v>
       </c>
       <c r="B9" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>130104769</v>
       </c>
       <c r="B10" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 58545-2025 artfynd.xlsx
+++ b/artfynd/A 58545-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130104789</v>
       </c>
       <c r="B2" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130104763</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130104751</v>
       </c>
       <c r="B4" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130104750</v>
       </c>
       <c r="B5" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>130104757</v>
       </c>
       <c r="B6" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>130104743</v>
       </c>
       <c r="B7" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>130104765</v>
       </c>
       <c r="B8" t="n">
-        <v>91414</v>
+        <v>91501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>130104791</v>
       </c>
       <c r="B9" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>130104769</v>
       </c>
       <c r="B10" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 58545-2025 artfynd.xlsx
+++ b/artfynd/A 58545-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130104789</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130104751</v>
       </c>
       <c r="B4" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130104750</v>
       </c>
       <c r="B5" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>130104757</v>
       </c>
       <c r="B6" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>130104743</v>
       </c>
       <c r="B7" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>130104765</v>
       </c>
       <c r="B8" t="n">
-        <v>91501</v>
+        <v>91504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>130104791</v>
       </c>
       <c r="B9" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>130104769</v>
       </c>
       <c r="B10" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 58545-2025 artfynd.xlsx
+++ b/artfynd/A 58545-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1556,6 +1556,345 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132867734</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97359</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>53</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>632976</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6661174</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132867732</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99119</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>633049</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6661077</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132867733</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99119</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>632990</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6661080</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58545-2025 artfynd.xlsx
+++ b/artfynd/A 58545-2025 artfynd.xlsx
@@ -1561,7 +1561,7 @@
         <v>132867734</v>
       </c>
       <c r="B11" t="n">
-        <v>97359</v>
+        <v>97361</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>132867732</v>
       </c>
       <c r="B12" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>132867733</v>
       </c>
       <c r="B13" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 58545-2025 artfynd.xlsx
+++ b/artfynd/A 58545-2025 artfynd.xlsx
@@ -1561,7 +1561,7 @@
         <v>132867734</v>
       </c>
       <c r="B11" t="n">
-        <v>97361</v>
+        <v>97362</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>132867732</v>
       </c>
       <c r="B12" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>132867733</v>
       </c>
       <c r="B13" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 58545-2025 artfynd.xlsx
+++ b/artfynd/A 58545-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130104789</v>
+        <v>130104743</v>
       </c>
       <c r="B2" t="n">
-        <v>98923</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633098</v>
+        <v>632971</v>
       </c>
       <c r="R2" t="n">
-        <v>6661062</v>
+        <v>6661174</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>12 12 buketter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130104763</v>
+        <v>130104750</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633102</v>
+        <v>632966</v>
       </c>
       <c r="R3" t="n">
-        <v>6661087</v>
+        <v>6661098</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -877,7 +872,7 @@
         <v>130104751</v>
       </c>
       <c r="B4" t="n">
-        <v>97169</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130104750</v>
+        <v>132867734</v>
       </c>
       <c r="B5" t="n">
-        <v>97169</v>
+        <v>97435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,17 +997,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långmossen N, Upl</t>
+          <t>Långmossen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632966</v>
+        <v>632976</v>
       </c>
       <c r="R5" t="n">
-        <v>6661098</v>
+        <v>6661174</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1036,12 +1031,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,7 +1076,7 @@
         <v>130104757</v>
       </c>
       <c r="B6" t="n">
-        <v>91731</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130104743</v>
+        <v>130104768</v>
       </c>
       <c r="B7" t="n">
-        <v>97169</v>
+        <v>92369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632971</v>
+        <v>633065</v>
       </c>
       <c r="R7" t="n">
-        <v>6661174</v>
+        <v>6661129</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1265,7 +1270,7 @@
         <v>130104765</v>
       </c>
       <c r="B8" t="n">
-        <v>91504</v>
+        <v>91680</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130104791</v>
+        <v>130104761</v>
       </c>
       <c r="B9" t="n">
-        <v>98923</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633109</v>
+        <v>633122</v>
       </c>
       <c r="R9" t="n">
-        <v>6661106</v>
+        <v>6661132</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1430,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>10 5 buketter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130104769</v>
+        <v>130104763</v>
       </c>
       <c r="B10" t="n">
-        <v>97794</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633082</v>
+        <v>633102</v>
       </c>
       <c r="R10" t="n">
-        <v>6661102</v>
+        <v>6661087</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1558,48 +1558,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132867734</v>
+        <v>130104773</v>
       </c>
       <c r="B11" t="n">
-        <v>97372</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långmossen, Upl</t>
+          <t>Långmossen N, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632976</v>
+        <v>633133</v>
       </c>
       <c r="R11" t="n">
-        <v>6661174</v>
+        <v>6661098</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1623,22 +1623,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>9 20 buketter</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1665,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132867732</v>
+        <v>130104785</v>
       </c>
       <c r="B12" t="n">
-        <v>99132</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1693,29 +1688,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långmossen, Upl</t>
+          <t>Långmossen N, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633049</v>
+        <v>633125</v>
       </c>
       <c r="R12" t="n">
-        <v>6661077</v>
+        <v>6661041</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1739,22 +1725,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>17:20</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>17:20</t>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>17 30 buketter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1781,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132867733</v>
+        <v>130104789</v>
       </c>
       <c r="B13" t="n">
-        <v>99132</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1809,29 +1790,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långmossen, Upl</t>
+          <t>Långmossen N, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>632990</v>
+        <v>633098</v>
       </c>
       <c r="R13" t="n">
-        <v>6661080</v>
+        <v>6661062</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1855,22 +1827,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>17:24</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>17:24</t>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>12 12 buketter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1894,6 +1861,646 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130104790</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långmossen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>633112</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6661079</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>11 12 buketter</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130104791</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långmossen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>633109</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6661106</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>10 5 buketter</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132867732</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>633049</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6661077</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132867733</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>632990</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6661080</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130104769</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långmossen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>633082</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6661102</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132867735</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>632967</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6661224</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
